--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SoundCue" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$19]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$21]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$D$24]]></definedName>
   </definedNames>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="125">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -79,6 +79,18 @@
   </si>
   <si>
     <t xml:space="preserve">요구 점수 게이지가 채워지는 길이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoneyStepMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돈이 오가는 연출의 길이. 동전이 날아가 꽂히는 데 걸리는 시간입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitStopMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">배수를 곱할 때 연출의 시계가 멈추는 길이</t>
   </si>
   <si>
     <t xml:space="preserve">FastForwardScale</t>
@@ -581,14 +593,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.09375" customWidth="1"/>
     <col min="2" max="2" width="45.703125" customWidth="1"/>
     <col min="3" max="3" width="7.03125" customWidth="1"/>
     <col min="4" max="4" width="10.546875" customWidth="1"/>
-    <col min="5" max="5" width="28.125" customWidth="1"/>
+    <col min="5" max="5" width="46.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,7 +723,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="5">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>21</v>
@@ -725,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="6">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>23</v>
@@ -739,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="5">
-        <v>200000</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>25</v>
@@ -753,7 +765,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="6">
-        <v>3000000</v>
+        <v>20</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>27</v>
@@ -767,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="5">
-        <v>16000</v>
+        <v>200000</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>29</v>
@@ -781,7 +793,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="6">
-        <v>12</v>
+        <v>3000000</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>31</v>
@@ -795,7 +807,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="5">
-        <v>30</v>
+        <v>16000</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>33</v>
@@ -809,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>35</v>
@@ -823,7 +835,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="5">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>37</v>
@@ -837,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>39</v>
@@ -851,14 +863,42 @@
         <v>8</v>
       </c>
       <c r="D19" s="5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>41</v>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6">
+        <v>6</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5">
+        <v>40</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:E19"/>
+  <autoFilter ref="B2:E21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -876,10 +916,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -891,67 +931,67 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -965,10 +1005,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D6" s="6">
         <v>8000</v>
@@ -982,44 +1022,44 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D7" s="5">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="E7" s="5">
         <v>2000</v>
       </c>
       <c r="F7" s="5">
-        <v>3500</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D8" s="6">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E8" s="6">
         <v>1500</v>
       </c>
       <c r="F8" s="6">
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D9" s="5">
         <v>10000</v>
@@ -1050,10 +1090,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1063,261 +1103,261 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -11,7 +11,7 @@
     <sheet name="SoundCue" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$21]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$23]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$D$24]]></definedName>
   </definedNames>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="129">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -157,6 +157,18 @@
   </si>
   <si>
     <t xml:space="preserve">카드를 뽑을 때 장마다의 간격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayStaggerMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 카드가 판으로 올라갈 때 장마다의 간격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayLandMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마지막 장이 자리에 붙고 득점이 시작되기까지</t>
   </si>
   <si>
     <t xml:space="preserve">:table EditionVisual(key=edition)</t>
@@ -593,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.09375" customWidth="1"/>
@@ -639,7 +651,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>9</v>
@@ -653,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="6">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>11</v>
@@ -667,7 +679,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="5">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>13</v>
@@ -681,7 +693,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="6">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>15</v>
@@ -695,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="5">
-        <v>400</v>
+        <v>620</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>17</v>
@@ -709,7 +721,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="6">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>19</v>
@@ -891,14 +903,42 @@
         <v>8</v>
       </c>
       <c r="D21" s="5">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="6">
+        <v>90</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="5">
+        <v>260</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:E21"/>
+  <autoFilter ref="B2:E23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -916,10 +956,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -931,67 +971,67 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -1005,10 +1045,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6">
         <v>8000</v>
@@ -1022,10 +1062,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D7" s="5">
         <v>9000</v>
@@ -1039,10 +1079,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6">
         <v>10000</v>
@@ -1056,10 +1096,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D9" s="5">
         <v>10000</v>
@@ -1090,10 +1130,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1103,261 +1143,261 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -903,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="5">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>45</v>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -108,13 +108,13 @@
     <t xml:space="preserve">ShakeThresholdMult</t>
   </si>
   <si>
-    <t xml:space="preserve">흔들림이 시작되는 배수. 만분율</t>
+    <t xml:space="preserve">세기가 오르기 시작하는 배수. 만분율</t>
   </si>
   <si>
     <t xml:space="preserve">ShakeMaxMult</t>
   </si>
   <si>
-    <t xml:space="preserve">흔들림이 최대가 되는 배수. 만분율</t>
+    <t xml:space="preserve">세기가 최대가 되는 배수. 만분율</t>
   </si>
   <si>
     <t xml:space="preserve">NumberScaleMaxBp</t>
@@ -791,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="5">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>29</v>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -13,13 +13,13 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$23]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$D$24]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$D$42]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="165">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -406,6 +406,114 @@
   </si>
   <si>
     <t xml:space="preserve">패배할 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드를 손패 자리에 놓을 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_slam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낸 카드가 판에 붙을 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_flip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뒷면이 앞면으로 뒤집힐 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coin_land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">동전이 꽂힐 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coin_lose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돈이 나갈 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joker_buy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커를 살 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joker_sell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커를 팔 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joker_burn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커가 타 사라질 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">joker_move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조커의 자리를 바꿀 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consumable_use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소모품을 쓸 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pack_open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팩을 뜯을 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pack_pick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">팩에서 고를 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">voucher_buy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바우처를 살 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blind_select</t>
+  </si>
+  <si>
+    <t xml:space="preserve">블라인드를 고를 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blind_skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">블라인드를 건너뛸 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">버튼을 누를 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel_open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판이 뜰 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">panel_close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판이 닫힐 때</t>
   </si>
 </sst>
 </file>
@@ -1119,12 +1227,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.984375" customWidth="1"/>
     <col min="2" max="2" width="50.390625" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="19.921875" customWidth="1"/>
     <col min="4" max="4" width="24.609375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1400,8 +1508,206 @@
         <v>94</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:D24"/>
+  <autoFilter ref="B2:D42"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -13,13 +13,13 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$23]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$D$42]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$E$42]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="178">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -267,12 +267,18 @@
     <t xml:space="preserve">pitch_follows_value</t>
   </si>
   <si>
+    <t xml:space="preserve">gain</t>
+  </si>
+  <si>
     <t xml:space="preserve">string (regex="^[a-z][a-z0-9_]*$")</t>
   </si>
   <si>
     <t xml:space="preserve">bool</t>
   </si>
   <si>
+    <t xml:space="preserve">float (min=0, max=4)</t>
+  </si>
+  <si>
     <t xml:space="preserve">식별자</t>
   </si>
   <si>
@@ -282,6 +288,9 @@
     <t xml:space="preserve">음높이가 값을 따라가는가</t>
   </si>
   <si>
+    <t xml:space="preserve">이 소리의 크기. 다 같은 크기로 맞춘 다음 곱합니다</t>
+  </si>
+  <si>
     <t xml:space="preserve">card_chip</t>
   </si>
   <si>
@@ -291,12 +300,18 @@
     <t xml:space="preserve">true</t>
   </si>
   <si>
+    <t xml:space="preserve">0.9</t>
+  </si>
+  <si>
     <t xml:space="preserve">card_mult</t>
   </si>
   <si>
     <t xml:space="preserve">카드의 배수가 더해질 때</t>
   </si>
   <si>
+    <t xml:space="preserve">1.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">joker_add</t>
   </si>
   <si>
@@ -330,30 +345,45 @@
     <t xml:space="preserve">재발동할 때</t>
   </si>
   <si>
+    <t xml:space="preserve">0.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">score_count</t>
   </si>
   <si>
     <t xml:space="preserve">점수를 세는 동안</t>
   </si>
   <si>
+    <t xml:space="preserve">0.7</t>
+  </si>
+  <si>
     <t xml:space="preserve">score_settle</t>
   </si>
   <si>
     <t xml:space="preserve">점수가 확정될 때</t>
   </si>
   <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">blind_clear</t>
   </si>
   <si>
     <t xml:space="preserve">요구 점수를 넘겼을 때</t>
   </si>
   <si>
+    <t xml:space="preserve">1.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">blind_fail</t>
   </si>
   <si>
     <t xml:space="preserve">넘기지 못했을 때</t>
   </si>
   <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
     <t xml:space="preserve">card_draw</t>
   </si>
   <si>
@@ -402,6 +432,9 @@
     <t xml:space="preserve">승리할 때</t>
   </si>
   <si>
+    <t xml:space="preserve">1.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">run_lose</t>
   </si>
   <si>
@@ -420,6 +453,9 @@
     <t xml:space="preserve">낸 카드가 판에 붙을 때</t>
   </si>
   <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">card_flip</t>
   </si>
   <si>
@@ -508,6 +544,9 @@
   </si>
   <si>
     <t xml:space="preserve">판이 뜰 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6</t>
   </si>
   <si>
     <t xml:space="preserve">panel_close</t>
@@ -1227,13 +1266,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.984375" customWidth="1"/>
     <col min="2" max="2" width="50.390625" customWidth="1"/>
     <col min="3" max="3" width="19.921875" customWidth="1"/>
     <col min="4" max="4" width="24.609375" customWidth="1"/>
+    <col min="5" max="5" width="36.328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1245,6 +1285,7 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -1259,19 +1300,25 @@
       <c r="D2" s="4" t="s">
         <v>81</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -1279,435 +1326,552 @@
         <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:D42"/>
+  <autoFilter ref="B2:E42"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -388,6 +388,9 @@
   </si>
   <si>
     <t xml:space="preserve">카드를 뽑을 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
   </si>
   <si>
     <t xml:space="preserve">card_select</t>
@@ -1503,15 +1506,15 @@
         <v>99</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>99</v>
@@ -1522,10 +1525,10 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>99</v>
@@ -1536,10 +1539,10 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>99</v>
@@ -1550,10 +1553,10 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>99</v>
@@ -1564,10 +1567,10 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>99</v>
@@ -1578,10 +1581,10 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>99</v>
@@ -1592,24 +1595,24 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>99</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>99</v>
@@ -1620,10 +1623,10 @@
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>99</v>
@@ -1634,24 +1637,24 @@
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>99</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>99</v>
@@ -1662,10 +1665,10 @@
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>92</v>
@@ -1676,10 +1679,10 @@
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>99</v>
@@ -1690,10 +1693,10 @@
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>99</v>
@@ -1704,10 +1707,10 @@
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>99</v>
@@ -1718,10 +1721,10 @@
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>99</v>
@@ -1732,10 +1735,10 @@
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>99</v>
@@ -1746,10 +1749,10 @@
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>99</v>
@@ -1760,24 +1763,24 @@
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>99</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>99</v>
@@ -1788,10 +1791,10 @@
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>99</v>
@@ -1802,10 +1805,10 @@
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>99</v>
@@ -1816,10 +1819,10 @@
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>99</v>
@@ -1830,10 +1833,10 @@
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>99</v>
@@ -1844,30 +1847,30 @@
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>99</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -9,17 +9,21 @@
     <sheet name="Const_Feel" sheetId="1" r:id="rId3"/>
     <sheet name="EditionVisual" sheetId="2" r:id="rId4"/>
     <sheet name="SoundCue" sheetId="3" r:id="rId5"/>
+    <sheet name="CardSet" sheetId="4" r:id="rId6"/>
+    <sheet name="CardSetSuit" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$23]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$E$42]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[CardSet!$B$2:$H$21]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[CardSetSuit!$B$2:$D$72]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="266">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -556,6 +560,267 @@
   </si>
   <si>
     <t xml:space="preserve">판이 닫힐 때</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table CardSet(key=set_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트럼프 한 벌의 겉모습입니다. **덱과 다른 축입니다** — 덱은 런의 시작 조건이고 이것은 그 52장이 어떻게 보이는가입니다. 그림이 있으면 그림이 얼굴이고, 없으면 무늬와 랭크를 그립니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sort_order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">art_dir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">art_has_index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (text=CardSet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int (min=1, max=99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (regex="^#[0-9a-f]{6}$")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">표시 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고르는 화면에서의 순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림이 있는 폴더. 비면 그립니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림이 어디서 왔는가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림에 모서리의 랭크와 무늬가 들어 있는가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종이의 색. **강화의 색과 겹치지 않아야 합니다** — 바탕에 색이 들면 강화로 읽힙니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">classic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정본</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">위키미디어 공용의 English pattern 한 벌 · Dmitry Fomin · 공유 재산</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#f6f2e8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">four_color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고양이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/cats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geckos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">게코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/geckos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest_kin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숲의 아이들</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/forest_kin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/dragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone_court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뼈의 궁정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/bone_court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tin_kings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">양철 왕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/tin_kings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/baseball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basketball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">농구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/basketball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soccer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/soccer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강아지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/dogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수달</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/otters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">squirrels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다람쥐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/squirrels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곤충</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/bugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">꽃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card/blooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table CardSetSuit(key="set_id,suit")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">세트가 무늬마다 쓰는 색입니다. **그림이 없는 세트에서만 보입니다** — 그림이 얼굴인 세트는 색이 그림 안에 있습니다. 네 색을 다 적는 것이 요점입니다. 빠진 것을 코드의 기본값으로 채우면 그 기본값이 어느 세트의 색인지가 코드에만 있게 됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign CardSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuitKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 색을 가진 세트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무늬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">카드에 쓰는 색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1f2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#d7343f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2f8b52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2f6fc0</t>
   </si>
 </sst>
 </file>
@@ -1877,4 +2142,1325 @@
   <autoFilter ref="B2:E42"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="32.8125" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="3" max="3" width="26.953125" customWidth="1"/>
+    <col min="4" max="4" width="24.609375" customWidth="1"/>
+    <col min="5" max="5" width="23.4375" customWidth="1"/>
+    <col min="6" max="6" width="53.90625" customWidth="1"/>
+    <col min="7" max="7" width="29.296875" customWidth="1"/>
+    <col min="8" max="8" width="53.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="6">
+        <v>6</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" s="6">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="6">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" s="5">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="6">
+        <v>12</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="5">
+        <v>13</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="6">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="5">
+        <v>15</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="6">
+        <v>16</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D21" s="5">
+        <v>17</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:H21"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D72"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="45.703125" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="3" max="3" width="11.71875" customWidth="1"/>
+    <col min="4" max="4" width="38.671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:D72"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -16,14 +16,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$23]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$E$42]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[CardSet!$B$2:$H$21]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[CardSet!$B$2:$I$21]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[CardSetSuit!$B$2:$D$72]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="274">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">세기. 만분율</t>
   </si>
   <si>
-    <t xml:space="preserve">흐르는 속도. 만분율</t>
+    <t xml:space="preserve">흐르는 속도. 만분율 — 초당 라디안입니다</t>
   </si>
   <si>
     <t xml:space="preserve">노이즈. 만분율</t>
@@ -586,6 +586,9 @@
     <t xml:space="preserve">paper</t>
   </si>
   <si>
+    <t xml:space="preserve">back</t>
+  </si>
+  <si>
     <t xml:space="preserve">string (text=CardSet)</t>
   </si>
   <si>
@@ -598,6 +601,9 @@
     <t xml:space="preserve">string (regex="^#[0-9a-f]{6}$")</t>
   </si>
   <si>
+    <t xml:space="preserve">CardBackKind?</t>
+  </si>
+  <si>
     <t xml:space="preserve">표시 이름</t>
   </si>
   <si>
@@ -616,6 +622,9 @@
     <t xml:space="preserve">종이의 색. **강화의 색과 겹치지 않아야 합니다** — 바탕에 색이 들면 강화로 읽힙니다</t>
   </si>
   <si>
+    <t xml:space="preserve">뒷면의 무늬. **색 두 개는 덱이 정합니다** — 비면 무늬도 덱의 것입니다</t>
+  </si>
+  <si>
     <t xml:space="preserve">classic</t>
   </si>
   <si>
@@ -631,15 +640,15 @@
     <t xml:space="preserve">#f6f2e8</t>
   </si>
   <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
     <t xml:space="preserve">line</t>
   </si>
   <si>
     <t xml:space="preserve">선화</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">four_color</t>
   </si>
   <si>
@@ -673,6 +682,9 @@
     <t xml:space="preserve">card/forest_kin</t>
   </si>
   <si>
+    <t xml:space="preserve">Brush</t>
+  </si>
+  <si>
     <t xml:space="preserve">dragons</t>
   </si>
   <si>
@@ -682,6 +694,9 @@
     <t xml:space="preserve">card/dragons</t>
   </si>
   <si>
+    <t xml:space="preserve">Zodiac</t>
+  </si>
+  <si>
     <t xml:space="preserve">bone_court</t>
   </si>
   <si>
@@ -691,6 +706,9 @@
     <t xml:space="preserve">card/bone_court</t>
   </si>
   <si>
+    <t xml:space="preserve">Arcane</t>
+  </si>
+  <si>
     <t xml:space="preserve">tin_kings</t>
   </si>
   <si>
@@ -700,6 +718,9 @@
     <t xml:space="preserve">card/tin_kings</t>
   </si>
   <si>
+    <t xml:space="preserve">Checker</t>
+  </si>
+  <si>
     <t xml:space="preserve">baseball</t>
   </si>
   <si>
@@ -761,6 +782,9 @@
   </si>
   <si>
     <t xml:space="preserve">card/bugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worn</t>
   </si>
   <si>
     <t xml:space="preserve">blooms</t>
@@ -1366,7 +1390,9 @@
     <col min="1" max="1" width="41.015625" customWidth="1"/>
     <col min="2" max="2" width="53.90625" customWidth="1"/>
     <col min="3" max="3" width="11.71875" customWidth="1"/>
-    <col min="4" max="6" width="15.234375" customWidth="1"/>
+    <col min="4" max="4" width="15.234375" customWidth="1"/>
+    <col min="5" max="5" width="29.296875" customWidth="1"/>
+    <col min="6" max="6" width="15.234375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1469,7 +1495,7 @@
         <v>8000</v>
       </c>
       <c r="E6" s="6">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
@@ -1486,7 +1512,7 @@
         <v>9000</v>
       </c>
       <c r="E7" s="5">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="F7" s="5">
         <v>1400</v>
@@ -1503,7 +1529,7 @@
         <v>10000</v>
       </c>
       <c r="E8" s="6">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="6">
         <v>1200</v>
@@ -1520,7 +1546,7 @@
         <v>10000</v>
       </c>
       <c r="E9" s="5">
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="5">
         <v>0</v>
@@ -2146,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.8125" customWidth="1"/>
@@ -2157,6 +2183,7 @@
     <col min="6" max="6" width="53.90625" customWidth="1"/>
     <col min="7" max="7" width="29.296875" customWidth="1"/>
     <col min="8" max="8" width="53.90625" customWidth="1"/>
+    <col min="9" max="9" width="52.734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2172,6 +2199,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -2198,6 +2226,9 @@
       <c r="H2" s="4" t="s">
         <v>186</v>
       </c>
+      <c r="I2" s="4" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -2207,22 +2238,25 @@
         <v>83</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>84</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="4">
@@ -2233,417 +2267,471 @@
         <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>201</v>
+      <c r="I6" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>201</v>
+      <c r="I7" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>201</v>
+      <c r="I8" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>201</v>
+      <c r="I9" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>201</v>
+      <c r="I10" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>201</v>
+      <c r="I11" s="5" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>201</v>
+      <c r="I12" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>201</v>
+      <c r="I13" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>201</v>
+      <c r="I14" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>201</v>
+      <c r="I15" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F16" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>201</v>
+      <c r="I16" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>201</v>
+      <c r="I17" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F18" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>201</v>
+      <c r="I18" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>201</v>
+      <c r="I19" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>201</v>
+      <c r="I20" s="6" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>201</v>
+      <c r="I21" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H21"/>
+  <autoFilter ref="B2:I21"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2661,10 +2749,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2677,10 +2765,10 @@
         <v>181</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -2688,13 +2776,13 @@
         <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4">
@@ -2702,761 +2790,761 @@
         <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -13,7 +13,7 @@
     <sheet name="CardSetSuit" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$23]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$27]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$E$42]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[CardSet!$B$2:$I$21]]></definedName>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="282">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -160,7 +160,19 @@
     <t xml:space="preserve">DrawStaggerMs</t>
   </si>
   <si>
-    <t xml:space="preserve">카드를 뽑을 때 장마다의 간격</t>
+    <t xml:space="preserve">카드를 뽑을 때 장마다의 간격. 뒷면으로 자리에 붙는 간격입니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DrawLandMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마지막 장이 뒷면으로 자리에 붙기까지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlipStaggerMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다 붙은 뒤 왼쪽부터 뒤집는 장마다의 간격</t>
   </si>
   <si>
     <t xml:space="preserve">PlayStaggerMs</t>
@@ -173,6 +185,18 @@
   </si>
   <si>
     <t xml:space="preserve">마지막 장이 자리에 붙고 득점이 시작되기까지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TagGainMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">건너뛰어 받은 태그 칩이 커져서 머리띠로 날아가 앉기까지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TagUseMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">받자마자 쓰이는 태그가 발동하는 시간</t>
   </si>
   <si>
     <t xml:space="preserve">:table EditionVisual(key=edition)</t>
@@ -1044,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.09375" customWidth="1"/>
@@ -1342,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="5">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>45</v>
@@ -1356,7 +1380,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>47</v>
@@ -1370,14 +1394,70 @@
         <v>8</v>
       </c>
       <c r="D23" s="5">
-        <v>260</v>
+        <v>25</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>49</v>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="6">
+        <v>90</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="5">
+        <v>260</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="6">
+        <v>760</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="5">
+        <v>300</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:E23"/>
+  <autoFilter ref="B2:E27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1397,10 +1477,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1412,67 +1492,67 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -1486,10 +1566,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D6" s="6">
         <v>8000</v>
@@ -1503,10 +1583,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5">
         <v>9000</v>
@@ -1520,10 +1600,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D8" s="6">
         <v>10000</v>
@@ -1537,10 +1617,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D9" s="5">
         <v>10000</v>
@@ -1572,10 +1652,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1586,582 +1666,582 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2188,10 +2268,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2206,528 +2286,528 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>204</v>
-      </c>
       <c r="I8" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2749,10 +2829,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2762,789 +2842,789 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -9,21 +9,23 @@
     <sheet name="Const_Feel" sheetId="1" r:id="rId3"/>
     <sheet name="EditionVisual" sheetId="2" r:id="rId4"/>
     <sheet name="SoundCue" sheetId="3" r:id="rId5"/>
-    <sheet name="CardSet" sheetId="4" r:id="rId6"/>
-    <sheet name="CardSetSuit" sheetId="5" r:id="rId7"/>
+    <sheet name="Transition" sheetId="4" r:id="rId6"/>
+    <sheet name="CardSet" sheetId="5" r:id="rId7"/>
+    <sheet name="CardSetSuit" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Const_Feel!$B$2:$E$27]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[EditionVisual!$B$2:$F$9]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[SoundCue!$B$2:$E$42]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[CardSet!$B$2:$I$21]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[CardSetSuit!$B$2:$D$72]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Transition!$B$2:$J$13]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[CardSet!$B$2:$I$21]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[CardSetSuit!$B$2:$D$72]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="327">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -586,6 +588,153 @@
     <t xml:space="preserve">판이 닫힐 때</t>
   </si>
   <si>
+    <t xml:space="preserve">:table Transition(key=transition_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">씬이 갈릴 때 화면을 어떻게 지우는가입니다. **덮개를 그리는 것이 아니라 화면 자체를 처리합니다.**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transition_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">out_ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hold_ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in_ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TransitionKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int (min=0, max=2000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (regex="^#[0-9a-f]{6}$")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">갈리는 자리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지우는 방법</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지우는 시간. 밀리초</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아무것도 보이지 않는 채로 머무는 시간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">되돌리는 시간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다 지워진 자리에 남는 색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다가오는가. 밀림과 옆으로가 이 값을 봅니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작할 때 나는 소리. `SoundCue` 의 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 자리인가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title_run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#05070d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판으로 들어갑니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판에서 나옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_lost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">진 판이 그 자리에서 타 없어집니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_won</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#f4ecd8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이긴 판만 밝은 쪽으로 나갑니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_restart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">접고 곧바로 펴는 것이므로 짧고 건조합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">login_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인 화면에서 타이틀로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title_login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">타이틀에서 로그인 화면으로</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boot_first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로딩에서 첫 화면으로. **지울 앞 화면이 없으므로 되돌리기만 합니다**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quiet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전환을 줄였을 때. **0이 아닙니다** — 갈아 끼우는 프레임은 어느 설정에서도 보이면 안 됩니다</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table CardSet(key=set_id)</t>
   </si>
   <si>
@@ -619,12 +768,6 @@
     <t xml:space="preserve">int (min=1, max=99)</t>
   </si>
   <si>
-    <t xml:space="preserve">string?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string (regex="^#[0-9a-f]{6}$")</t>
-  </si>
-  <si>
     <t xml:space="preserve">CardBackKind?</t>
   </si>
   <si>
@@ -664,9 +807,6 @@
     <t xml:space="preserve">#f6f2e8</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">line</t>
   </si>
   <si>
@@ -827,9 +967,6 @@
   </si>
   <si>
     <t xml:space="preserve">suit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ink</t>
   </si>
   <si>
     <t xml:space="preserve">foreign CardSet</t>
@@ -2252,6 +2389,400 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="44.53125" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="6" width="26.953125" customWidth="1"/>
+    <col min="7" max="7" width="38.671875" customWidth="1"/>
+    <col min="8" max="8" width="30.46875" customWidth="1"/>
+    <col min="9" max="9" width="35.15625" customWidth="1"/>
+    <col min="10" max="10" width="53.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="5">
+        <v>340</v>
+      </c>
+      <c r="E5" s="5">
+        <v>70</v>
+      </c>
+      <c r="F5" s="5">
+        <v>420</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="6">
+        <v>300</v>
+      </c>
+      <c r="E6" s="6">
+        <v>60</v>
+      </c>
+      <c r="F6" s="6">
+        <v>360</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="5">
+        <v>520</v>
+      </c>
+      <c r="E7" s="5">
+        <v>80</v>
+      </c>
+      <c r="F7" s="5">
+        <v>340</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="6">
+        <v>300</v>
+      </c>
+      <c r="E8" s="6">
+        <v>60</v>
+      </c>
+      <c r="F8" s="6">
+        <v>380</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="5">
+        <v>260</v>
+      </c>
+      <c r="E9" s="5">
+        <v>60</v>
+      </c>
+      <c r="F9" s="5">
+        <v>300</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="6">
+        <v>260</v>
+      </c>
+      <c r="E10" s="6">
+        <v>50</v>
+      </c>
+      <c r="F10" s="6">
+        <v>300</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="5">
+        <v>260</v>
+      </c>
+      <c r="E11" s="5">
+        <v>50</v>
+      </c>
+      <c r="F11" s="5">
+        <v>300</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>520</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="5">
+        <v>120</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>120</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:J13"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
@@ -2268,10 +2799,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2286,28 +2817,28 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -2318,16 +2849,16 @@
         <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>92</v>
@@ -2336,7 +2867,7 @@
         <v>199</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -2347,48 +2878,48 @@
         <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>213</v>
@@ -2396,10 +2927,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
@@ -2414,7 +2945,7 @@
         <v>107</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>213</v>
@@ -2422,10 +2953,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
@@ -2440,7 +2971,7 @@
         <v>107</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>213</v>
@@ -2448,16 +2979,16 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>213</v>
@@ -2466,7 +2997,7 @@
         <v>107</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>213</v>
@@ -2474,16 +3005,16 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>213</v>
@@ -2492,7 +3023,7 @@
         <v>107</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>213</v>
@@ -2500,16 +3031,16 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>213</v>
@@ -2518,24 +3049,24 @@
         <v>107</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>213</v>
@@ -2544,24 +3075,24 @@
         <v>107</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>213</v>
@@ -2570,24 +3101,24 @@
         <v>107</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>213</v>
@@ -2596,24 +3127,24 @@
         <v>107</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>213</v>
@@ -2622,7 +3153,7 @@
         <v>107</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>213</v>
@@ -2630,16 +3161,16 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>213</v>
@@ -2648,7 +3179,7 @@
         <v>107</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>213</v>
@@ -2656,16 +3187,16 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>213</v>
@@ -2674,7 +3205,7 @@
         <v>107</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>213</v>
@@ -2682,16 +3213,16 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>213</v>
@@ -2700,7 +3231,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>213</v>
@@ -2708,16 +3239,16 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>253</v>
+        <v>299</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>213</v>
@@ -2726,7 +3257,7 @@
         <v>107</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>213</v>
@@ -2734,16 +3265,16 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>213</v>
@@ -2752,7 +3283,7 @@
         <v>107</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>213</v>
@@ -2760,16 +3291,16 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>213</v>
@@ -2778,24 +3309,24 @@
         <v>107</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>213</v>
@@ -2804,10 +3335,10 @@
         <v>107</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2816,7 +3347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D72"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
@@ -2829,10 +3360,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2842,13 +3373,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>268</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3">
@@ -2856,10 +3387,10 @@
         <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>199</v>
@@ -2870,761 +3401,761 @@
         <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -681,10 +681,10 @@
     <t xml:space="preserve">run_lost</t>
   </si>
   <si>
-    <t xml:space="preserve">Burn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">진 판이 그 자리에서 타 없어집니다</t>
+    <t xml:space="preserve">Ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">진 판이 조각으로 부서져 흩어집니다</t>
   </si>
   <si>
     <t xml:space="preserve">run_won</t>
@@ -2580,10 +2580,10 @@
         <v>218</v>
       </c>
       <c r="D7" s="5">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="E7" s="5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F7" s="5">
         <v>340</v>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">:const FeelConst</t>
   </si>
   <si>
-    <t xml:space="preserve">연출의 길이와 문턱입니다. **두 런타임이 같은 값을 읽습니다.**</t>
+    <t xml:space="preserve">연출의 길이와 문턱입니다. **연출 수치도 데이터입니다.**</t>
   </si>
   <si>
     <t xml:space="preserve">:field</t>
@@ -204,7 +204,7 @@
     <t xml:space="preserve">:table EditionVisual(key=edition)</t>
   </si>
   <si>
-    <t xml:space="preserve">에디션 셰이더의 파라미터입니다. 웹 GLSL과 유니티 HLSL이 같은 수식에 이 값을 넣습니다.</t>
+    <t xml:space="preserve">에디션 셰이더의 파라미터입니다. 값이 코드가 아니라 여기 있어야 기획이 고칠 수 있습니다.</t>
   </si>
   <si>
     <t xml:space="preserve">edition</t>
@@ -1209,7 +1209,7 @@
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.09375" customWidth="1"/>
-    <col min="2" max="2" width="45.703125" customWidth="1"/>
+    <col min="2" max="2" width="41.015625" customWidth="1"/>
     <col min="3" max="3" width="7.03125" customWidth="1"/>
     <col min="4" max="4" width="10.546875" customWidth="1"/>
     <col min="5" max="5" width="46.875" customWidth="1"/>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -2580,13 +2580,13 @@
         <v>218</v>
       </c>
       <c r="D7" s="5">
-        <v>600</v>
+        <v>1150</v>
       </c>
       <c r="E7" s="5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F7" s="5">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>212</v>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="326">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -702,10 +702,7 @@
     <t xml:space="preserve">run_restart</t>
   </si>
   <si>
-    <t xml:space="preserve">Blocks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">접고 곧바로 펴는 것이므로 짧고 건조합니다</t>
+    <t xml:space="preserve">접고 곧바로 펴는 것이므로 진 판과 같은 몸짓을 짧게 씁니다</t>
   </si>
   <si>
     <t xml:space="preserve">login_title</t>
@@ -2522,13 +2519,13 @@
         <v>211</v>
       </c>
       <c r="D5" s="5">
-        <v>340</v>
+        <v>510</v>
       </c>
       <c r="E5" s="5">
         <v>70</v>
       </c>
       <c r="F5" s="5">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>212</v>
@@ -2551,13 +2548,13 @@
         <v>211</v>
       </c>
       <c r="D6" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="E6" s="6">
         <v>60</v>
       </c>
       <c r="F6" s="6">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>212</v>
@@ -2580,13 +2577,13 @@
         <v>218</v>
       </c>
       <c r="D7" s="5">
-        <v>1150</v>
+        <v>1725</v>
       </c>
       <c r="E7" s="5">
         <v>80</v>
       </c>
       <c r="F7" s="5">
-        <v>380</v>
+        <v>456</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>212</v>
@@ -2609,13 +2606,13 @@
         <v>221</v>
       </c>
       <c r="D8" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="E8" s="6">
         <v>60</v>
       </c>
       <c r="F8" s="6">
-        <v>380</v>
+        <v>456</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>222</v>
@@ -2635,16 +2632,16 @@
         <v>224</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D9" s="5">
-        <v>260</v>
+        <v>840</v>
       </c>
       <c r="E9" s="5">
         <v>60</v>
       </c>
       <c r="F9" s="5">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>212</v>
@@ -2653,27 +2650,27 @@
         <v>100</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="D10" s="6">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E10" s="6">
         <v>50</v>
       </c>
       <c r="F10" s="6">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>212</v>
@@ -2685,24 +2682,24 @@
         <v>213</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D11" s="5">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E11" s="5">
         <v>50</v>
       </c>
       <c r="F11" s="5">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>212</v>
@@ -2714,12 +2711,12 @@
         <v>213</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>221</v>
@@ -2731,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6">
-        <v>520</v>
+        <v>624</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>212</v>
@@ -2743,12 +2740,12 @@
         <v>213</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>221</v>
@@ -2772,7 +2769,7 @@
         <v>213</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2799,10 +2796,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2817,28 +2814,28 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -2849,10 +2846,10 @@
         <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>200</v>
@@ -2867,7 +2864,7 @@
         <v>199</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -2878,48 +2875,48 @@
         <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>213</v>
@@ -2927,10 +2924,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
@@ -2945,7 +2942,7 @@
         <v>107</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>213</v>
@@ -2953,10 +2950,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>263</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
@@ -2971,7 +2968,7 @@
         <v>107</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>213</v>
@@ -2979,16 +2976,16 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>213</v>
@@ -2997,7 +2994,7 @@
         <v>107</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>213</v>
@@ -3005,16 +3002,16 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>213</v>
@@ -3023,7 +3020,7 @@
         <v>107</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>213</v>
@@ -3031,16 +3028,16 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>213</v>
@@ -3049,24 +3046,24 @@
         <v>107</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>213</v>
@@ -3075,24 +3072,24 @@
         <v>107</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>213</v>
@@ -3101,24 +3098,24 @@
         <v>107</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>213</v>
@@ -3127,24 +3124,24 @@
         <v>107</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>213</v>
@@ -3153,7 +3150,7 @@
         <v>107</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>213</v>
@@ -3161,16 +3158,16 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>290</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>213</v>
@@ -3179,7 +3176,7 @@
         <v>107</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>213</v>
@@ -3187,16 +3184,16 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>293</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>213</v>
@@ -3205,7 +3202,7 @@
         <v>107</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>213</v>
@@ -3213,16 +3210,16 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>213</v>
@@ -3231,7 +3228,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>213</v>
@@ -3239,16 +3236,16 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>213</v>
@@ -3257,7 +3254,7 @@
         <v>107</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>213</v>
@@ -3265,16 +3262,16 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>301</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>302</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>213</v>
@@ -3283,7 +3280,7 @@
         <v>107</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>213</v>
@@ -3291,16 +3288,16 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>304</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>305</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>213</v>
@@ -3309,24 +3306,24 @@
         <v>107</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>309</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>213</v>
@@ -3335,10 +3332,10 @@
         <v>107</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -3360,10 +3357,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3373,10 +3370,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>194</v>
@@ -3387,10 +3384,10 @@
         <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>199</v>
@@ -3401,761 +3398,761 @@
         <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C18" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C22" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C38" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C46" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C49" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C54" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C57" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C65" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C69" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>319</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="327">
   <si>
     <t xml:space="preserve">:const FeelConst</t>
   </si>
@@ -619,6 +619,9 @@
   </si>
   <si>
     <t xml:space="preserve">TransitionKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int (min=0, max=4000)</t>
   </si>
   <si>
     <t xml:space="preserve">int (min=0, max=2000)</t>
@@ -2461,19 +2464,19 @@
         <v>198</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>92</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>67</v>
@@ -2484,39 +2487,39 @@
         <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5" s="5">
         <v>510</v>
@@ -2528,24 +2531,24 @@
         <v>504</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D6" s="6">
         <v>450</v>
@@ -2557,27 +2560,27 @@
         <v>432</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>107</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D7" s="5">
-        <v>1725</v>
+        <v>3450</v>
       </c>
       <c r="E7" s="5">
         <v>80</v>
@@ -2586,7 +2589,7 @@
         <v>456</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>100</v>
@@ -2595,15 +2598,15 @@
         <v>164</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" s="6">
         <v>450</v>
@@ -2615,7 +2618,7 @@
         <v>456</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>100</v>
@@ -2624,18 +2627,18 @@
         <v>174</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9" s="5">
-        <v>840</v>
+        <v>1680</v>
       </c>
       <c r="E9" s="5">
         <v>60</v>
@@ -2644,7 +2647,7 @@
         <v>360</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>100</v>
@@ -2653,15 +2656,15 @@
         <v>164</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10" s="6">
         <v>390</v>
@@ -2673,24 +2676,24 @@
         <v>360</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D11" s="5">
         <v>390</v>
@@ -2702,24 +2705,24 @@
         <v>360</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>107</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D12" s="6">
         <v>0</v>
@@ -2731,24 +2734,24 @@
         <v>624</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>100</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D13" s="5">
         <v>120</v>
@@ -2760,16 +2763,16 @@
         <v>120</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>100</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2796,10 +2799,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2814,28 +2817,28 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -2846,25 +2849,25 @@
         <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>92</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -2875,467 +2878,467 @@
         <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D10" s="6">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D11" s="5">
         <v>7</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D13" s="5">
         <v>9</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D14" s="6">
         <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D15" s="5">
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D16" s="6">
         <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D18" s="6">
         <v>14</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D19" s="5">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D20" s="6">
         <v>16</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>107</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D21" s="5">
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>107</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -3357,10 +3360,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3370,10 +3373,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>194</v>
@@ -3384,13 +3387,13 @@
         <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -3398,761 +3401,761 @@
         <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Feel.xlsx
+++ b/samples/clover/design-data/xlsx/Feel.xlsx
@@ -651,7 +651,7 @@
     <t xml:space="preserve">다 지워진 자리에 남는 색</t>
   </si>
   <si>
-    <t xml:space="preserve">다가오는가. 밀림과 옆으로가 이 값을 봅니다</t>
+    <t xml:space="preserve">다가오는가. 밀림과 옆으로가 이 값을 씁니다</t>
   </si>
   <si>
     <t xml:space="preserve">시작할 때 나는 소리. `SoundCue` 의 이름</t>
